--- a/rsvp_export.xlsx
+++ b/rsvp_export.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="62" uniqueCount="47">
   <si>
     <t>Event Name</t>
   </si>
@@ -35,19 +35,124 @@
     <t>Attendees</t>
   </si>
   <si>
+    <t>Tech Talk AI</t>
+  </si>
+  <si>
+    <t>Pune</t>
+  </si>
+  <si>
+    <t>2026-04-20T10:00</t>
+  </si>
+  <si>
+    <t>OPEN</t>
+  </si>
+  <si>
+    <t>juiyi, prasad, sanjay, yeti, j, ram</t>
+  </si>
+  <si>
+    <t>ted talk</t>
+  </si>
+  <si>
+    <t>2030-07-21T22:22</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>Resume Workshop</t>
+  </si>
+  <si>
+    <t>Chennai</t>
+  </si>
+  <si>
+    <t>2026-04-24T10:30</t>
+  </si>
+  <si>
+    <t>sanjay</t>
+  </si>
+  <si>
+    <t>Startup Pitch</t>
+  </si>
+  <si>
+    <t>Jaipur</t>
+  </si>
+  <si>
+    <t>2026-04-25T16:00</t>
+  </si>
+  <si>
+    <t>Placement Talk</t>
+  </si>
+  <si>
+    <t>Kochi</t>
+  </si>
+  <si>
+    <t>2026-04-30T15:00</t>
+  </si>
+  <si>
+    <t>Coding Contest</t>
+  </si>
+  <si>
+    <t>Mumbai</t>
+  </si>
+  <si>
+    <t>2026-04-20T14:00</t>
+  </si>
+  <si>
+    <t>juiyi, prasad, j, ram</t>
+  </si>
+  <si>
+    <t>Project Expo</t>
+  </si>
+  <si>
+    <t>Delhi</t>
+  </si>
+  <si>
+    <t>2026-04-23T11:00</t>
+  </si>
+  <si>
+    <t>ram</t>
+  </si>
+  <si>
+    <t>DJ Night</t>
+  </si>
+  <si>
+    <t>Bangalore</t>
+  </si>
+  <si>
+    <t>2026-04-21T19:00</t>
+  </si>
+  <si>
+    <t>juiyi, sanjay</t>
+  </si>
+  <si>
+    <t>Alumni Meet</t>
+  </si>
+  <si>
+    <t>Lucknow</t>
+  </si>
+  <si>
+    <t>2026-04-30T11:00</t>
+  </si>
+  <si>
     <t>m</t>
   </si>
   <si>
-    <t>Pune</t>
-  </si>
-  <si>
     <t>2030-09-21T22:22</t>
   </si>
   <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>Jay</t>
+    <t>san, Jay, prasad, rawat</t>
+  </si>
+  <si>
+    <t>Hackathon</t>
+  </si>
+  <si>
+    <t>Hyderabad</t>
+  </si>
+  <si>
+    <t>2026-04-22T09:00</t>
+  </si>
+  <si>
+    <t>sanjay, prasas</t>
   </si>
 </sst>
 </file>
@@ -92,16 +197,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G12"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="11.91796875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="8.6640625" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="17.91015625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="10.83984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="17.42578125" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="14.625" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="13.8359375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="6.59375" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="10.2421875" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="29.0859375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -138,16 +243,246 @@
         <v>9</v>
       </c>
       <c r="D2" t="n" s="0">
-        <v>500.0</v>
+        <v>50.0</v>
       </c>
       <c r="E2" t="n" s="0">
-        <v>1.0</v>
+        <v>6.0</v>
       </c>
       <c r="F2" t="s" s="0">
         <v>10</v>
       </c>
       <c r="G2" t="s" s="0">
         <v>11</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="0">
+        <v>12</v>
+      </c>
+      <c r="B3" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s" s="0">
+        <v>13</v>
+      </c>
+      <c r="D3" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="E3" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F3" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G3" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="0">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s" s="0">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s" s="0">
+        <v>17</v>
+      </c>
+      <c r="D4" t="n" s="0">
+        <v>35.0</v>
+      </c>
+      <c r="E4" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F4" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s" s="0">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="s" s="0">
+        <v>19</v>
+      </c>
+      <c r="B5" t="s" s="0">
+        <v>20</v>
+      </c>
+      <c r="C5" t="s" s="0">
+        <v>21</v>
+      </c>
+      <c r="D5" t="n" s="0">
+        <v>30.0</v>
+      </c>
+      <c r="E5" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F5" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G5" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="s" s="0">
+        <v>22</v>
+      </c>
+      <c r="B6" t="s" s="0">
+        <v>23</v>
+      </c>
+      <c r="C6" t="s" s="0">
+        <v>24</v>
+      </c>
+      <c r="D6" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="E6" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F6" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G6" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="s" s="0">
+        <v>25</v>
+      </c>
+      <c r="B7" t="s" s="0">
+        <v>26</v>
+      </c>
+      <c r="C7" t="s" s="0">
+        <v>27</v>
+      </c>
+      <c r="D7" t="n" s="0">
+        <v>40.0</v>
+      </c>
+      <c r="E7" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F7" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G7" t="s" s="0">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="s" s="0">
+        <v>29</v>
+      </c>
+      <c r="B8" t="s" s="0">
+        <v>30</v>
+      </c>
+      <c r="C8" t="s" s="0">
+        <v>31</v>
+      </c>
+      <c r="D8" t="n" s="0">
+        <v>150.0</v>
+      </c>
+      <c r="E8" t="n" s="0">
+        <v>1.0</v>
+      </c>
+      <c r="F8" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G8" t="s" s="0">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="s" s="0">
+        <v>33</v>
+      </c>
+      <c r="B9" t="s" s="0">
+        <v>34</v>
+      </c>
+      <c r="C9" t="s" s="0">
+        <v>35</v>
+      </c>
+      <c r="D9" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="E9" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F9" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G9" t="s" s="0">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="s" s="0">
+        <v>37</v>
+      </c>
+      <c r="B10" t="s" s="0">
+        <v>38</v>
+      </c>
+      <c r="C10" t="s" s="0">
+        <v>39</v>
+      </c>
+      <c r="D10" t="n" s="0">
+        <v>200.0</v>
+      </c>
+      <c r="E10" t="n" s="0">
+        <v>0.0</v>
+      </c>
+      <c r="F10" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G10" t="s" s="0">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="s" s="0">
+        <v>40</v>
+      </c>
+      <c r="B11" t="s" s="0">
+        <v>8</v>
+      </c>
+      <c r="C11" t="s" s="0">
+        <v>41</v>
+      </c>
+      <c r="D11" t="n" s="0">
+        <v>500.0</v>
+      </c>
+      <c r="E11" t="n" s="0">
+        <v>4.0</v>
+      </c>
+      <c r="F11" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G11" t="s" s="0">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="s" s="0">
+        <v>43</v>
+      </c>
+      <c r="B12" t="s" s="0">
+        <v>44</v>
+      </c>
+      <c r="C12" t="s" s="0">
+        <v>45</v>
+      </c>
+      <c r="D12" t="n" s="0">
+        <v>60.0</v>
+      </c>
+      <c r="E12" t="n" s="0">
+        <v>2.0</v>
+      </c>
+      <c r="F12" t="s" s="0">
+        <v>10</v>
+      </c>
+      <c r="G12" t="s" s="0">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
